--- a/questionnaire_templates/003_pet_retail_expansion_interest_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/003_pet_retail_expansion_interest_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'north'}</t>
+          <t>north</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'North'}</t>
+          <t>North</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'south'}</t>
+          <t>south</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'South'}</t>
+          <t>South</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'east'}</t>
+          <t>east</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'East'}</t>
+          <t>East</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'west'}</t>
+          <t>west</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'West'}</t>
+          <t>West</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'cat'}</t>
+          <t>cat</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Cat'}</t>
+          <t>Cat</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'dog'}</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Dog'}</t>
+          <t>Dog</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'bird'}</t>
+          <t>bird</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Bird'}</t>
+          <t>Bird</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'fish'}</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Fish'}</t>
+          <t>Fish</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
